--- a/Egne applikasjoner/Flytting/Manuell kontroll 2025.xlsx
+++ b/Egne applikasjoner/Flytting/Manuell kontroll 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://telemarkfylke-my.sharepoint.com/personal/even_sannes_riiser_telemarkfylke_no/Documents/Github/Telemark/Egne applikasjoner/Flytting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{2EF9139E-5A99-4B85-86F9-80EE34F0C78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0792FB19-C9A3-4B8F-AB94-99759135E03A}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{2EF9139E-5A99-4B85-86F9-80EE34F0C78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E97DF34-45F6-4149-A6EF-D008BDCDAB4E}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="38610" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19740" yWindow="0" windowWidth="37290" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Til kommunene" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="418">
   <si>
     <t>13864: Innenlandske flyttinger, etter fraflyttingsregion, år og tilflyttingsregion</t>
   </si>
@@ -1281,6 +1281,15 @@
   <si>
     <t>Alle tall stemmer med kartløsning!</t>
   </si>
+  <si>
+    <t>Ekstern + intern</t>
+  </si>
+  <si>
+    <t>Ekstern</t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
 </sst>
 </file>
 
@@ -42724,6 +42733,7 @@
   <dimension ref="C1:Z17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
     <col min="4" max="4" width="40.28515625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="13" bestFit="1" customWidth="1"/>
   </cols>
@@ -42788,7 +42798,9 @@
       </c>
     </row>
     <row r="2" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>415</v>
+      </c>
       <c r="D2" t="s">
         <v>383</v>
       </c>
@@ -42855,7 +42867,9 @@
       </c>
     </row>
     <row r="3" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>416</v>
+      </c>
       <c r="D3" t="s">
         <v>384</v>
       </c>
@@ -42920,7 +42934,9 @@
       <c r="Z3" s="10"/>
     </row>
     <row r="4" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>417</v>
+      </c>
       <c r="D4" t="s">
         <v>385</v>
       </c>
@@ -43010,7 +43026,9 @@
       <c r="Z5" s="10"/>
     </row>
     <row r="6" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>415</v>
+      </c>
       <c r="D6" t="s">
         <v>387</v>
       </c>
@@ -43075,7 +43093,9 @@
       <c r="Z6" s="10"/>
     </row>
     <row r="7" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>416</v>
+      </c>
       <c r="D7" t="s">
         <v>388</v>
       </c>
@@ -43140,7 +43160,9 @@
       <c r="Z7" s="10"/>
     </row>
     <row r="8" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>417</v>
+      </c>
       <c r="D8" t="s">
         <v>389</v>
       </c>
